--- a/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2000.xlsx
+++ b/Immigration_Networks/MigrationData/Matrices/DifferenceMatrices_2000.xlsx
@@ -9,10 +9,10 @@
     <sheet name="RawMatrix" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="DiffMat" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="DiffMat_Pos" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DiffMat_PopScaled" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="DiffMat_PopScaled_Per1000" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DiffMat_PopScaled_Pos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="DiffMat_PopScaled_Per1000_Pos" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DiffMat_PopScaled_dest" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DiffMat_PopScaled_org" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="DiffMat_PopScaled_Per1000_dest" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="DiffMat_PopScaled_Per1000_org" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="DM_10000_binary" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
@@ -4230,19 +4230,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0230112155885352</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0000306174728849321</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0.000407486750044559</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0103314487429205</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0000266053148107132</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>0.000219161356088191</v>
@@ -4263,22 +4263,22 @@
         <v>0.000036775487505505</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.000000394166338194718</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0.000161314352715593</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.0456117176128093</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.00300557244174265</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.0004229699162083</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0276104285286185</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0.000263595653908548</v>
@@ -4304,43 +4304,43 @@
         <v>0.000398616221203364</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0000171655444596044</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0.0000358073594535746</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.00000819594292944278</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0000106000556923561</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.00000470182239216413</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0000134155744024672</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0000750486657155578</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000007686243594797</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0.0000324037564406869</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.00038136826783115</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.000203101862676331</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0.000181130178259826</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.000135750674258316</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0.0000557407530717782</v>
@@ -4354,7 +4354,7 @@
         <v>0.000143171989947972</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.000654867205224065</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4363,22 +4363,22 @@
         <v>0.00039075091831807</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.000663457354578933</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0000583270363157942</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0.0000446957110909868</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0000070926429197101</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0000476161231894726</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000000598413759002708</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0.00000616808018504241</v>
@@ -4387,7 +4387,7 @@
         <v>0.0000218498712375804</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0000776507686243595</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0.0000855881827726838</v>
@@ -4396,13 +4396,13 @@
         <v>0.0098830058224163</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.000284272465123529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.000724325276938463</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.00398321845969434</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0.000114537562875677</v>
@@ -4413,61 +4413,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.000338259949223925</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0000842403697280779</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0000693662753742522</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.00161059013648026</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.000439038858443711</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.000356041971304338</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000810925507153521</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00649076743561938</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.00117195060316687</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.000648111025443331</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.000359927902400462</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.00182577847851793</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.000724505728244488</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.000436135371179039</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.000663977866105526</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.00208107466943245</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0017635600839077</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.000301043109640167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -4478,7 +4478,7 @@
         <v>0.00430416169105038</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.000718076530923478</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0.0000591087323750773</v>
@@ -4490,13 +4490,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0000550525360313988</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0.000336995503509883</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00032744368145995</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0.0000348287544177415</v>
@@ -4520,13 +4520,13 @@
         <v>0.000215429403202329</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.00117765567765568</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.000266400725748762</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.000234641893916692</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0.000503130241433217</v>
@@ -4588,7 +4588,7 @@
         <v>0.0018042341025151</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.000109080011986815</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0.0249674239417424</v>
@@ -4599,58 +4599,58 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0000231902078312875</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0000163832994919434</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00000101138799319596</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0.0000453842090532627</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0000855928358473891</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.000132335859149826</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0000458657575474586</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.00135260075731509</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.000110706545415501</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.000363145720894372</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0.0000082167825639915</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0439765471028774</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.00203721007883623</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0000114628820960699</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.000102914815680773</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.000227512495064972</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0000716212166616722</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0.00000533733851806988</v>
@@ -4661,7 +4661,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.00000631483063772024</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
         <v>0.000012084135795476</v>
@@ -4676,7 +4676,7 @@
         <v>0.000268001682702262</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.00152448453865386</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0.000147800590084968</v>
@@ -4685,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0000201905822711545</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00000632608830945719</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
         <v>0.0000226676946800308</v>
@@ -4697,22 +4697,22 @@
         <v>0.00000862710878441555</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0000151754040204967</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
         <v>0.000526913256905082</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0000183770014556041</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.000107980671810459</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.00104858930207089</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.000119268804315253</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
         <v>0.00108933357431704</v>
@@ -4723,7 +4723,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.000000268716197349797</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>0.00000732019764533642</v>
@@ -4735,10 +4735,10 @@
         <v>0.00124877791201692</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0000133517083801127</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0000012279376066483</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>0.00204152739466161</v>
@@ -4753,28 +4753,28 @@
         <v>0.00049796573517011</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.000455050115651503</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0.0000446024601600937</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.000481474182104848</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0.000591016340298615</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0000027292576419214</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00000362403553892916</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.00296169907967292</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0000200779142942763</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0.0000313783853199431</v>
@@ -4785,7 +4785,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00000400387134051198</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0.00000639064873799212</v>
@@ -4797,10 +4797,10 @@
         <v>0.000443774694658473</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0000123196922734373</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0000098235008531864</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0.000328869010584249</v>
@@ -4809,34 +4809,34 @@
         <v>0.00000583172862287275</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.00098008451441229</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.000288974556669237</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0.000185529000564732</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.000828734726054395</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0.000144408045007409</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.00000691411935953421</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00000658561296859169</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.00173196893919125</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0000266706622715013</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>0.0000111051075617906</v>
@@ -4847,28 +4847,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0000000806148592049392</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>0.0000101088443673693</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000000229860907544536</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0.000136055514016308</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0000148352315334585</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00000915836798291857</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0.000598059088745874</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0000115846501021932</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0.00049652006901814</v>
@@ -4889,16 +4889,16 @@
         <v>0.000190900391204916</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.00000473071324599709</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00000639077234821916</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.00101261839936512</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0000149835181300569</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>0.0000101581604053588</v>
@@ -4909,58 +4909,58 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0000963347567499023</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0.00085007247576637</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0000122400933267465</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0.00113580295510116</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.000257036511568836</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.00011263769337651</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.000203416276044775</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0000662768077275133</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.00073157209762483</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00154613017790328</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.000468619892058597</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.000585534095388254</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.000019371810915628</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0.000270014556040757</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.00017110903281116</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.0321656907547204</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.000408750374587953</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0.00000391691778342225</v>
@@ -4983,10 +4983,10 @@
         <v>0.000299885387068064</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00000715961174006043</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00000790484834279843</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>0.0566662891233495</v>
@@ -5001,7 +5001,7 @@
         <v>0.000359475693800912</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.00065520431765613</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0.0000304769800219959</v>
@@ -5016,13 +5016,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.00000264983243706648</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.00079213094377948</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.00000629307761462391</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>0.0000778648820902292</v>
@@ -5033,61 +5033,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0000123072018386207</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0000106898124344595</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00000139640501333305</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0.0000665872453798584</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0000683710670672437</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.000501791586550133</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0.00146886359630834</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.000117895486754292</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.000282331642091643</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0000350499487415872</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0000835774865073246</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0.000000564198553083062</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.000901852581789515</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.00000636826783114993</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.0000952770633621697</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.000364701531088344</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0000791129757267006</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.000000559559683346036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5101,13 +5101,13 @@
         <v>0.000243541813724209</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.000312133872877413</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0.000077593401640992</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0000763691918939779</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5128,7 +5128,7 @@
         <v>0.00000400925212027756</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0000152231027777321</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -5146,7 +5146,7 @@
         <v>0.0000373211884934075</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.00064219358705424</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0.000010287289563054</v>
@@ -5172,7 +5172,7 @@
         <v>0.00194928492248979</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0000138910441752089</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0.000670689619268727</v>
@@ -5199,7 +5199,7 @@
         <v>0.000861165048885645</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0000724163027656478</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -5208,7 +5208,7 @@
         <v>0.000988057411564827</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.000102786934372191</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0.0014628611844768</v>
@@ -5219,61 +5219,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.00319860951191384</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.00592285325037109</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.00117137693136964</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0189584278702809</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.00483570497084748</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.01298930307736</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0162598425796739</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0232556728337197</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.140238232045314</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.041667891990078</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0439434078643022</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0928581572421778</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0439343713046906</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0361495602422815</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.00191102620087336</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.0108355155482815</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.00748216961342523</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.00428661456190372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -5343,58 +5343,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.000164561799257016</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.00015047072937636</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0000152914968744002</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0.000226403108501084</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.00075395226693303</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0148390375895749</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0000314901600868316</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.00199445118902248</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.000122657787297263</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0000220558214032426</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0000363916730917502</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.000000933492151464703</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.000356523452897123</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0.00000457879167096662</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0000434861717612809</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.0013243706647962</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0.000353877924485381</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.00120857057237039</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -5481,58 +5481,58 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-23.0112155885352</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0306174728849321</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.407486750044559</v>
+        <v>0.000338259949223925</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.3314487429205</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0266053148107132</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.219161356088191</v>
+        <v>0.0000231902078312875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0185196787347986</v>
+        <v>0.00000631483063772024</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00168254852259621</v>
+        <v>0.000000268716197349797</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0127376642987719</v>
+        <v>0.00000400387134051198</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00046260601387818</v>
+        <v>0.0000000806148592049392</v>
       </c>
       <c r="M2" t="n">
-        <v>0.036775487505505</v>
+        <v>0.0000963347567499023</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.000394166338194718</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.161314352715593</v>
+        <v>0.0000123072018386207</v>
       </c>
       <c r="P2" t="n">
-        <v>-45.6117176128093</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.00557244174265</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4229699162083</v>
+        <v>0.00319860951191384</v>
       </c>
       <c r="S2" t="n">
-        <v>-27.6104285286185</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.263595653908548</v>
+        <v>0.000164561799257016</v>
       </c>
     </row>
     <row r="3">
@@ -5540,61 +5540,61 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>5.32170931555485</v>
+        <v>0.0230112155885352</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0323874018730251</v>
+        <v>0.000654867205224065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0234690096744761</v>
+        <v>0.0000842403697280779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.398616221203364</v>
+        <v>0.000718076530923478</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0171655444596044</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0358073594535746</v>
+        <v>0.0000163832994919434</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.00819594292944278</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0106000556923561</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.00470182239216413</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0134155744024672</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0750486657155578</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.007686243594797</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0324037564406869</v>
+        <v>0.0000106898124344595</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.38136826783115</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.203101862676331</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.181130178259826</v>
+        <v>0.00592285325037109</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.135750674258316</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0557407530717782</v>
+        <v>0.00015047072937636</v>
       </c>
     </row>
     <row r="4">
@@ -5602,61 +5602,61 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.143171989947972</v>
+        <v>0.0000306174728849321</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.654867205224065</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.39075091831807</v>
+        <v>0.0000693662753742522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.663457354578933</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0583270363157942</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0446957110909868</v>
+        <v>0.00000101138799319596</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0070926429197101</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.0476161231894726</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000598413759002708</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00616808018504241</v>
+        <v>0.000000229860907544536</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0218498712375804</v>
+        <v>0.0000122400933267465</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0776507686243595</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0855881827726838</v>
+        <v>0.00000139640501333305</v>
       </c>
       <c r="P4" t="n">
-        <v>9.8830058224163</v>
+        <v>0.000312133872877413</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.284272465123529</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.724325276938463</v>
+        <v>0.00117137693136964</v>
       </c>
       <c r="S4" t="n">
-        <v>-3.98321845969434</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.114537562875677</v>
+        <v>0.0000152914968744002</v>
       </c>
     </row>
     <row r="5">
@@ -5664,61 +5664,61 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.338259949223925</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.0842403697280779</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0693662753742522</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.61059013648026</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.439038858443711</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.356041971304338</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.810925507153521</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-6.49076743561938</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.17195060316687</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.648111025443331</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.359927902400462</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.82577847851793</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.724505728244488</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.436135371179039</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.663977866105526</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08107466943245</v>
+        <v>0.0189584278702809</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7635600839077</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.301043109640167</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -5726,61 +5726,61 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4.30416169105038</v>
+        <v>0.0103314487429205</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.718076530923478</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0591087323750773</v>
+        <v>0.000663457354578933</v>
       </c>
       <c r="E6" t="n">
-        <v>0.808305064236784</v>
+        <v>0.00161059013648026</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0550525360313988</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.336995503509883</v>
+        <v>0.0000855928358473891</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.32744368145995</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0348287544177415</v>
+        <v>0.0000133517083801127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0163281468527882</v>
+        <v>0.0000123196922734373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0354664610639938</v>
+        <v>0.0000148352315334585</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0408787497097455</v>
+        <v>0.000257036511568836</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0218762317698069</v>
+        <v>0.00000715961174006043</v>
       </c>
       <c r="O6" t="n">
-        <v>0.37334762855574</v>
+        <v>0.0000683710670672437</v>
       </c>
       <c r="P6" t="n">
-        <v>0.215429403202329</v>
+        <v>0.0000763691918939779</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.17765567765568</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.266400725748762</v>
+        <v>0.00483570497084748</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.234641893916692</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.503130241433217</v>
+        <v>0.00075395226693303</v>
       </c>
     </row>
     <row r="7">
@@ -5788,61 +5788,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0279464845243789</v>
+        <v>0.0000266053148107132</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0779659146035038</v>
+        <v>0.0000171655444596044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0131020717300385</v>
+        <v>0.0000583270363157942</v>
       </c>
       <c r="E7" t="n">
-        <v>0.555551922804633</v>
+        <v>0.000439038858443711</v>
       </c>
       <c r="F7" t="n">
-        <v>0.138806166347838</v>
+        <v>0.0000550525360313988</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.31369837200951</v>
+        <v>0.000132335859149826</v>
       </c>
       <c r="I7" t="n">
-        <v>4.69627529857071</v>
+        <v>0.00152448453865386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00807623290846179</v>
+        <v>0.0000012279376066483</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0328272690652914</v>
+        <v>0.0000098235008531864</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0552043176561295</v>
+        <v>0.00000915836798291857</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0451666587131768</v>
+        <v>0.00011263769337651</v>
       </c>
       <c r="N7" t="n">
-        <v>0.060898699251084</v>
+        <v>0.00000790484834279843</v>
       </c>
       <c r="O7" t="n">
-        <v>6.90869220200079</v>
+        <v>0.000501791586550133</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0211596913724573</v>
+        <v>0.0000138910441752089</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8042341025151</v>
+        <v>0.01298930307736</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.109080011986814</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>24.9674239417424</v>
+        <v>0.0148390375895749</v>
       </c>
     </row>
     <row r="8">
@@ -5850,61 +5850,61 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.0231902078312875</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0163832994919434</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.00101138799319596</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0453842090532627</v>
+        <v>0.000356041971304338</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0855928358473891</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.132335859149826</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0458657575474586</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.35260075731509</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.110706545415501</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.363145720894372</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0082167825639915</v>
+        <v>0.000203416276044775</v>
       </c>
       <c r="N8" t="n">
-        <v>-43.9765471028774</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.03721007883623</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.0114628820960699</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.102914815680773</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.227512495064972</v>
+        <v>0.0162598425796739</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0716212166616722</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00533733851806988</v>
+        <v>0.0000314901600868316</v>
       </c>
     </row>
     <row r="9">
@@ -5912,61 +5912,61 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.00631483063772024</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.012084135795476</v>
+        <v>0.00000819594292944278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000517187041975205</v>
+        <v>0.0000070926429197101</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333098082138426</v>
+        <v>0.000810925507153521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.268001682702262</v>
+        <v>0.00032744368145995</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.52448453865386</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.147800590084968</v>
+        <v>0.0000458657575474586</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0201905822711545</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.00632608830945719</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0226676946800308</v>
+        <v>0.0000115846501021932</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00862710878441555</v>
+        <v>0.0000662768077275133</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0151754040204966</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.526913256905082</v>
+        <v>0.000117895486754292</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.0183770014556041</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.107980671810459</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.04858930207089</v>
+        <v>0.0232556728337197</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.119268804315253</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.08933357431704</v>
+        <v>0.00199445118902248</v>
       </c>
     </row>
     <row r="10">
@@ -5974,61 +5974,61 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.000268716197349797</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00732019764533642</v>
+        <v>0.0000106000556923561</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00162626592087759</v>
+        <v>0.0000476161231894726</v>
       </c>
       <c r="E10" t="n">
-        <v>1.24877791201692</v>
+        <v>0.00649076743561938</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0133517083801127</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0012279376066483</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.04152739466161</v>
+        <v>0.00135260075731509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00945685722628013</v>
+        <v>0.0000201905822711545</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.49796573517011</v>
+        <v>0.00098008451441229</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.455050115651503</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0446024601600937</v>
+        <v>0.00073157209762483</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.481474182104848</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.591016340298615</v>
+        <v>0.000282331642091643</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.0027292576419214</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.00362403553892916</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.96169907967292</v>
+        <v>0.140238232045314</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0200779142942763</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0313783853199431</v>
+        <v>0.000122657787297263</v>
       </c>
     </row>
     <row r="11">
@@ -6036,61 +6036,61 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>-0.00400387134051198</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00639064873799212</v>
+        <v>0.00000470182239216413</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000402256588202937</v>
+        <v>0.000000598413759002708</v>
       </c>
       <c r="E11" t="n">
-        <v>0.443774694658473</v>
+        <v>0.00117195060316687</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0123196922734373</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0098235008531864</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.328869010584249</v>
+        <v>0.000110706545415501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00583172862287275</v>
+        <v>0.00000632608830945719</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.98008451441229</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.288974556669237</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.185529000564732</v>
+        <v>0.00154613017790328</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.828734726054395</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.144408045007409</v>
+        <v>0.0000350499487415872</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.00691411935953421</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.00658561296859169</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73196893919125</v>
+        <v>0.041667891990078</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0266706622715014</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0111051075617906</v>
+        <v>0.0000220558214032426</v>
       </c>
     </row>
     <row r="12">
@@ -6098,61 +6098,61 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.0000806148592049392</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0101088443673693</v>
+        <v>0.0000134155744024672</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.000229860907544536</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.136055514016308</v>
+        <v>0.000648111025443331</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0148352315334585</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.00915836798291857</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.598059088745874</v>
+        <v>0.000363145720894372</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0115846501021932</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.49652006901814</v>
+        <v>0.000455050115651503</v>
       </c>
       <c r="K12" t="n">
-        <v>0.160203912053011</v>
+        <v>0.000288974556669237</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0311745345967168</v>
+        <v>0.000468619892058597</v>
       </c>
       <c r="N12" t="n">
-        <v>0.837406385494679</v>
+        <v>0.00065520431765613</v>
       </c>
       <c r="O12" t="n">
-        <v>0.190900391204916</v>
+        <v>0.0000835774865073246</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.00473071324599709</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.00639077234821916</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.01261839936512</v>
+        <v>0.0439434078643022</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0149835181300569</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0101581604053588</v>
+        <v>0.0000363916730917502</v>
       </c>
     </row>
     <row r="13">
@@ -6160,61 +6160,61 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0963347567499023</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.85007247576637</v>
+        <v>0.0000750486657155578</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0122400933267465</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.13580295510116</v>
+        <v>0.000359927902400462</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.257036511568836</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.11263769337651</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.203416276044775</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0662768077275133</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.73157209762483</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.54613017790328</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.468619892058597</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.585534095388254</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.019371810915628</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.270014556040757</v>
+        <v>0.0000152231027777321</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.17110903281116</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>32.1656907547204</v>
+        <v>0.0928581572421778</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.408750374587953</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.00391691778342225</v>
+        <v>0.000000933492151464703</v>
       </c>
     </row>
     <row r="14">
@@ -6222,61 +6222,61 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0000537432394699595</v>
+        <v>0.000000394166338194718</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0045315509233035</v>
+        <v>0.000007686243594797</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00226412993931367</v>
+        <v>0.0000776507686243595</v>
       </c>
       <c r="E14" t="n">
-        <v>0.299885387068064</v>
+        <v>0.00182577847851793</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.00715961174006043</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.00790484834279843</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>56.6662891233495</v>
+        <v>0.0439765471028774</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00606815005352975</v>
+        <v>0.0000151754040204967</v>
       </c>
       <c r="J14" t="n">
-        <v>0.411046604070253</v>
+        <v>0.000481474182104848</v>
       </c>
       <c r="K14" t="n">
-        <v>0.359475693800912</v>
+        <v>0.000828734726054395</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.65520431765613</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0304769800219959</v>
+        <v>0.000585534095388254</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.61173466818025</v>
+        <v>0.000901852581789515</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.00264983243706648</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.79213094377948</v>
+        <v>0.0439343713046906</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.00629307761462391</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0778648820902292</v>
+        <v>0.000356523452897123</v>
       </c>
     </row>
     <row r="15">
@@ -6284,61 +6284,61 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.0123072018386207</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0106898124344595</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.00139640501333305</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0665872453798584</v>
+        <v>0.000724505728244488</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0683710670672437</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.501791586550133</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.46886359630834</v>
+        <v>0.00203721007883623</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.117895486754292</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.282331642091643</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0350499487415872</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.0835774865073246</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000564198553083062</v>
+        <v>0.000019371810915628</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.901852581789515</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.00636826783114993</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.0952770633621697</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.364701531088344</v>
+        <v>0.0361495602422815</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0791129757267006</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.000559559683346036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -6346,61 +6346,61 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>6.73623137840419</v>
+        <v>0.0456117176128093</v>
       </c>
       <c r="C16" t="n">
-        <v>0.243541813724209</v>
+        <v>0.00038136826783115</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.312133872877413</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.077593401640992</v>
+        <v>0.000436135371179039</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0763691918939779</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0159990329473419</v>
+        <v>0.0000114628820960699</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00795952149878578</v>
+        <v>0.0000183770014556041</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00252382278389431</v>
+        <v>0.0000027292576419214</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00324853183458613</v>
+        <v>0.00000691411935953421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00400925212027756</v>
+        <v>0.00000473071324599709</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0152231027777321</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0123275160372178</v>
+        <v>0.00000636826783114993</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0155093133816538</v>
+        <v>0.0000724163027656478</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0373211884934075</v>
+        <v>0.00191102620087336</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.64219358705424</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.010287289563054</v>
+        <v>0.0000434861717612809</v>
       </c>
     </row>
     <row r="17">
@@ -6408,61 +6408,61 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.07258115853925</v>
+        <v>0.00300557244174265</v>
       </c>
       <c r="C17" t="n">
-        <v>0.605601113134816</v>
+        <v>0.000203101862676331</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0419208830134347</v>
+        <v>0.000284272465123529</v>
       </c>
       <c r="E17" t="n">
-        <v>0.551570283921929</v>
+        <v>0.000663977866105526</v>
       </c>
       <c r="F17" t="n">
-        <v>1.94928492248979</v>
+        <v>0.00117765567765568</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0138910441752089</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.670689619268727</v>
+        <v>0.000102914815680773</v>
       </c>
       <c r="I17" t="n">
-        <v>0.218374594783519</v>
+        <v>0.000107980671810459</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0156477012601447</v>
+        <v>0.00000362403553892916</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0144474178959225</v>
+        <v>0.00000658561296859169</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0252891287586739</v>
+        <v>0.00000639077234821916</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0450435608470496</v>
+        <v>0.00017110903281116</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0134016554986204</v>
+        <v>0.00000264983243706648</v>
       </c>
       <c r="O17" t="n">
-        <v>0.861165048885645</v>
+        <v>0.0000952770633621697</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.0724163027656478</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.988057411564827</v>
+        <v>0.0108355155482815</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.102786934372191</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4628611844768</v>
+        <v>0.0013243706647962</v>
       </c>
     </row>
     <row r="18">
@@ -6470,61 +6470,61 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>-3.19860951191384</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>-5.92285325037109</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.17137693136964</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>-18.9584278702809</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.83570497084748</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-12.98930307736</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>-16.2598425796739</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-23.2556728337197</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-140.238232045314</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-41.667891990078</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-43.9434078643022</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-92.8581572421778</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-43.9343713046906</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-36.1495602422815</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.91102620087336</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-10.8355155482815</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-7.48216961342523</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-4.28661456190372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -6532,61 +6532,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.47584355590209</v>
+        <v>0.0276104285286185</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0526357068783714</v>
+        <v>0.000135750674258316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0763827795770491</v>
+        <v>0.00398321845969434</v>
       </c>
       <c r="E19" t="n">
-        <v>0.190503616461092</v>
+        <v>0.0017635600839077</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0505042882204263</v>
+        <v>0.000234641893916692</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00931186018374961</v>
+        <v>0.000109080011986815</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0606947440383286</v>
+        <v>0.0000716212166616722</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0313652431338291</v>
+        <v>0.000119268804315253</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0112730751013946</v>
+        <v>0.0000200779142942763</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00760840350732014</v>
+        <v>0.0000266706622715013</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00771010023130301</v>
+        <v>0.0000149835181300569</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0139921241164599</v>
+        <v>0.000408750374587953</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00413874655104454</v>
+        <v>0.00000629307761462391</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0929846923950145</v>
+        <v>0.0000791129757267006</v>
       </c>
       <c r="P19" t="n">
-        <v>0.389919941775837</v>
+        <v>0.00064219358705424</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0133660665575559</v>
+        <v>0.000102786934372191</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0887208830147004</v>
+        <v>0.00748216961342523</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.173592630994966</v>
+        <v>0.00120857057237039</v>
       </c>
     </row>
     <row r="20">
@@ -6594,58 +6594,58 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>-0.164561799257016</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.15047072937636</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0152914968744002</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.226403108501084</v>
+        <v>0.000301043109640167</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.75395226693303</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-14.8390375895749</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0314901600868316</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.99445118902248</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.122657787297263</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0220558214032427</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0363916730917502</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.000933492151464703</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.356523452897123</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00457879167096662</v>
+        <v>0.000000559559683346036</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.0434861717612809</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3243706647962</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.353877924485381</v>
+        <v>0.00428661456190372</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.20857057237039</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000407486750044559</v>
+        <v>0.407486750044559</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -6747,28 +6747,28 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000219161356088191</v>
+        <v>0.219161356088191</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0000185196787347986</v>
+        <v>0.0185196787347986</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00000168254852259621</v>
+        <v>0.00168254852259621</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0000127376642987719</v>
+        <v>0.0127376642987719</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00000046260601387818</v>
+        <v>0.00046260601387818</v>
       </c>
       <c r="M2" t="n">
-        <v>0.000036775487505505</v>
+        <v>0.036775487505505</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000161314352715593</v>
+        <v>0.161314352715593</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -6777,13 +6777,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0004229699162083</v>
+        <v>0.4229699162083</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.000263595653908548</v>
+        <v>0.263595653908548</v>
       </c>
     </row>
     <row r="3">
@@ -6791,25 +6791,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00532170931555485</v>
+        <v>5.32170931555485</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0000323874018730251</v>
+        <v>0.0323874018730251</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0000234690096744761</v>
+        <v>0.0234690096744761</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000398616221203364</v>
+        <v>0.398616221203364</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0000358073594535746</v>
+        <v>0.0358073594535746</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -6830,7 +6830,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0000324037564406869</v>
+        <v>0.0324037564406869</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -6839,13 +6839,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.000181130178259826</v>
+        <v>0.181130178259826</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0000557407530717782</v>
+        <v>0.0557407530717782</v>
       </c>
     </row>
     <row r="4">
@@ -6853,7 +6853,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.000143171989947972</v>
+        <v>0.143171989947972</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00039075091831807</v>
+        <v>0.39075091831807</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -6871,7 +6871,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0000446957110909868</v>
+        <v>0.0446957110909868</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -6883,31 +6883,31 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00000616808018504241</v>
+        <v>0.00616808018504241</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0000218498712375804</v>
+        <v>0.0218498712375804</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0000855881827726838</v>
+        <v>0.0855881827726838</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0098830058224163</v>
+        <v>9.8830058224163</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.000724325276938463</v>
+        <v>0.724325276938463</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.000114537562875677</v>
+        <v>0.114537562875677</v>
       </c>
     </row>
     <row r="5">
@@ -6963,7 +6963,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.00208107466943245</v>
+        <v>2.08107466943245</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -6977,16 +6977,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.00430416169105038</v>
+        <v>4.30416169105038</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0000591087323750773</v>
+        <v>0.0591087323750773</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000808305064236784</v>
+        <v>0.808305064236784</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -6995,43 +6995,43 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.000336995503509883</v>
+        <v>0.336995503509883</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0000348287544177415</v>
+        <v>0.0348287544177415</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0000163281468527882</v>
+        <v>0.0163281468527882</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0000354664610639938</v>
+        <v>0.0354664610639938</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0000408787497097455</v>
+        <v>0.0408787497097455</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0000218762317698069</v>
+        <v>0.0218762317698069</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00037334762855574</v>
+        <v>0.37334762855574</v>
       </c>
       <c r="P6" t="n">
-        <v>0.000215429403202329</v>
+        <v>0.215429403202329</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.000266400725748762</v>
+        <v>0.266400725748762</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.000503130241433217</v>
+        <v>0.503130241433217</v>
       </c>
     </row>
     <row r="7">
@@ -7039,61 +7039,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0000279464845243789</v>
+        <v>0.0279464845243789</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0000779659146035038</v>
+        <v>0.0779659146035038</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0000131020717300385</v>
+        <v>0.0131020717300385</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000555551922804633</v>
+        <v>0.555551922804633</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000138806166347838</v>
+        <v>0.138806166347838</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00131369837200951</v>
+        <v>1.31369837200951</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00469627529857071</v>
+        <v>4.69627529857071</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00000807623290846179</v>
+        <v>0.00807623290846179</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0000328272690652914</v>
+        <v>0.0328272690652914</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0000552043176561295</v>
+        <v>0.0552043176561295</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0000451666587131768</v>
+        <v>0.0451666587131768</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000060898699251084</v>
+        <v>0.060898699251084</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00690869220200079</v>
+        <v>6.90869220200079</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0000211596913724573</v>
+        <v>0.0211596913724573</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0018042341025151</v>
+        <v>1.8042341025151</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0249674239417424</v>
+        <v>24.9674239417424</v>
       </c>
     </row>
     <row r="8">
@@ -7110,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0000453842090532627</v>
+        <v>0.0453842090532627</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -7134,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0000082167825639915</v>
+        <v>0.0082167825639915</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -7149,13 +7149,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000227512495064972</v>
+        <v>0.227512495064972</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00000533733851806988</v>
+        <v>0.00533733851806988</v>
       </c>
     </row>
     <row r="9">
@@ -7166,22 +7166,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000012084135795476</v>
+        <v>0.012084135795476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000000517187041975205</v>
+        <v>0.000517187041975205</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000333098082138426</v>
+        <v>0.333098082138426</v>
       </c>
       <c r="F9" t="n">
-        <v>0.000268001682702262</v>
+        <v>0.268001682702262</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000147800590084968</v>
+        <v>0.147800590084968</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -7193,16 +7193,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0000226676946800308</v>
+        <v>0.0226676946800308</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00000862710878441555</v>
+        <v>0.00862710878441555</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000526913256905082</v>
+        <v>0.526913256905082</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -7211,13 +7211,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.00104858930207089</v>
+        <v>1.04858930207089</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.00108933357431704</v>
+        <v>1.08933357431704</v>
       </c>
     </row>
     <row r="10">
@@ -7228,13 +7228,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00000732019764533642</v>
+        <v>0.00732019764533642</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00000162626592087759</v>
+        <v>0.00162626592087759</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00124877791201692</v>
+        <v>1.24877791201692</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -7243,28 +7243,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00204152739466161</v>
+        <v>2.04152739466161</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00000945685722628013</v>
+        <v>0.00945685722628013</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00049796573517011</v>
+        <v>0.49796573517011</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0000446024601600937</v>
+        <v>0.0446024601600937</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.000591016340298615</v>
+        <v>0.591016340298615</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -7273,13 +7273,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.00296169907967292</v>
+        <v>2.96169907967292</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0000313783853199431</v>
+        <v>0.0313783853199431</v>
       </c>
     </row>
     <row r="11">
@@ -7290,13 +7290,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00000639064873799212</v>
+        <v>0.00639064873799212</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000000402256588202937</v>
+        <v>0.0000402256588202937</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000443774694658473</v>
+        <v>0.443774694658473</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -7305,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.000328869010584249</v>
+        <v>0.328869010584249</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00000583172862287275</v>
+        <v>0.00583172862287275</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -7320,13 +7320,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.000185529000564732</v>
+        <v>0.185529000564732</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.000144408045007409</v>
+        <v>0.144408045007409</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -7335,13 +7335,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.00173196893919125</v>
+        <v>1.73196893919125</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0000111051075617906</v>
+        <v>0.0111051075617906</v>
       </c>
     </row>
     <row r="12">
@@ -7352,13 +7352,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0000101088443673693</v>
+        <v>0.0101088443673693</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.000136055514016308</v>
+        <v>0.136055514016308</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -7367,28 +7367,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.000598059088745874</v>
+        <v>0.598059088745874</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00049652006901814</v>
+        <v>0.49652006901814</v>
       </c>
       <c r="K12" t="n">
-        <v>0.000160203912053011</v>
+        <v>0.160203912053011</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0000311745345967168</v>
+        <v>0.0311745345967168</v>
       </c>
       <c r="N12" t="n">
-        <v>0.000837406385494679</v>
+        <v>0.837406385494679</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000190900391204916</v>
+        <v>0.190900391204916</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -7397,13 +7397,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.00101261839936512</v>
+        <v>1.01261839936512</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0000101581604053588</v>
+        <v>0.0101581604053588</v>
       </c>
     </row>
     <row r="13">
@@ -7414,13 +7414,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.00085007247576637</v>
+        <v>0.85007247576637</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.00113580295510116</v>
+        <v>1.13580295510116</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -7453,19 +7453,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.000270014556040757</v>
+        <v>0.270014556040757</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0321656907547204</v>
+        <v>32.1656907547204</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.00000391691778342225</v>
+        <v>0.00391691778342225</v>
       </c>
     </row>
     <row r="14">
@@ -7473,16 +7473,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0000000537432394699594</v>
+        <v>0.0000537432394699595</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0000045315509233035</v>
+        <v>0.0045315509233035</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00000226412993931367</v>
+        <v>0.00226412993931367</v>
       </c>
       <c r="E14" t="n">
-        <v>0.000299885387068064</v>
+        <v>0.299885387068064</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7491,28 +7491,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0566662891233495</v>
+        <v>56.6662891233495</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00000606815005352975</v>
+        <v>0.00606815005352975</v>
       </c>
       <c r="J14" t="n">
-        <v>0.000411046604070253</v>
+        <v>0.411046604070253</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000359475693800912</v>
+        <v>0.359475693800912</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0000304769800219959</v>
+        <v>0.0304769800219959</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00161173466818025</v>
+        <v>1.61173466818025</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -7521,13 +7521,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.00079213094377948</v>
+        <v>0.79213094377948</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0000778648820902292</v>
+        <v>0.0778648820902292</v>
       </c>
     </row>
     <row r="15">
@@ -7544,7 +7544,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0000665872453798584</v>
+        <v>0.0665872453798584</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -7553,7 +7553,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.00146886359630834</v>
+        <v>1.46886359630834</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000000564198553083062</v>
+        <v>0.000564198553083062</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.000364701531088344</v>
+        <v>0.364701531088344</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -7597,16 +7597,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.00673623137840419</v>
+        <v>6.73623137840419</v>
       </c>
       <c r="C16" t="n">
-        <v>0.000243541813724209</v>
+        <v>0.243541813724209</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000077593401640992</v>
+        <v>0.077593401640992</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -7615,19 +7615,19 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0000159990329473418</v>
+        <v>0.0159990329473419</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00000795952149878578</v>
+        <v>0.00795952149878578</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00000252382278389431</v>
+        <v>0.00252382278389431</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00000324853183458613</v>
+        <v>0.00324853183458613</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00000400925212027756</v>
+        <v>0.00400925212027756</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -7636,22 +7636,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0000123275160372178</v>
+        <v>0.0123275160372178</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0000155093133816538</v>
+        <v>0.0155093133816538</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0000373211884934075</v>
+        <v>0.0373211884934075</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.000010287289563054</v>
+        <v>0.010287289563054</v>
       </c>
     </row>
     <row r="17">
@@ -7659,46 +7659,46 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.00207258115853925</v>
+        <v>2.07258115853925</v>
       </c>
       <c r="C17" t="n">
-        <v>0.000605601113134817</v>
+        <v>0.605601113134816</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0000419208830134347</v>
+        <v>0.0419208830134347</v>
       </c>
       <c r="E17" t="n">
-        <v>0.000551570283921929</v>
+        <v>0.551570283921929</v>
       </c>
       <c r="F17" t="n">
-        <v>0.00194928492248979</v>
+        <v>1.94928492248979</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.000670689619268727</v>
+        <v>0.670689619268727</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000218374594783519</v>
+        <v>0.218374594783519</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0000156477012601447</v>
+        <v>0.0156477012601447</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0000144474178959225</v>
+        <v>0.0144474178959225</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0000252891287586739</v>
+        <v>0.0252891287586739</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0000450435608470495</v>
+        <v>0.0450435608470496</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0000134016554986204</v>
+        <v>0.0134016554986204</v>
       </c>
       <c r="O17" t="n">
-        <v>0.000861165048885645</v>
+        <v>0.861165048885645</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -7707,13 +7707,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.000988057411564827</v>
+        <v>0.988057411564827</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0014628611844768</v>
+        <v>1.4628611844768</v>
       </c>
     </row>
     <row r="18">
@@ -7783,61 +7783,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.00247584355590209</v>
+        <v>2.47584355590209</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0000526357068783714</v>
+        <v>0.0526357068783714</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0000763827795770491</v>
+        <v>0.0763827795770491</v>
       </c>
       <c r="E19" t="n">
-        <v>0.000190503616461092</v>
+        <v>0.190503616461092</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0000505042882204263</v>
+        <v>0.0505042882204263</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00000931186018374961</v>
+        <v>0.00931186018374961</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0000606947440383286</v>
+        <v>0.0606947440383286</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0000313652431338291</v>
+        <v>0.0313652431338291</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0000112730751013946</v>
+        <v>0.0112730751013946</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00000760840350732014</v>
+        <v>0.00760840350732014</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00000771010023130301</v>
+        <v>0.00771010023130301</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0000139921241164599</v>
+        <v>0.0139921241164599</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00000413874655104454</v>
+        <v>0.00413874655104454</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0000929846923950145</v>
+        <v>0.0929846923950145</v>
       </c>
       <c r="P19" t="n">
-        <v>0.000389919941775837</v>
+        <v>0.389919941775837</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0000133660665575559</v>
+        <v>0.0133660665575559</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0000887208830147004</v>
+        <v>0.0887208830147004</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.000173592630994966</v>
+        <v>0.173592630994966</v>
       </c>
     </row>
     <row r="20">
@@ -7854,7 +7854,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.000226403108501084</v>
+        <v>0.226403108501084</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -7884,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00000457879167096662</v>
+        <v>0.00457879167096662</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -7893,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.000353877924485381</v>
+        <v>0.353877924485381</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -7989,7 +7989,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.407486750044559</v>
+        <v>0.338259949223925</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -7998,28 +7998,28 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.219161356088191</v>
+        <v>0.0231902078312875</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0185196787347986</v>
+        <v>0.00631483063772024</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00168254852259621</v>
+        <v>0.000268716197349797</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0127376642987719</v>
+        <v>0.00400387134051198</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00046260601387818</v>
+        <v>0.0000806148592049392</v>
       </c>
       <c r="M2" t="n">
-        <v>0.036775487505505</v>
+        <v>0.0963347567499023</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.161314352715593</v>
+        <v>0.0123072018386207</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4229699162083</v>
+        <v>3.19860951191384</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.263595653908548</v>
+        <v>0.164561799257016</v>
       </c>
     </row>
     <row r="3">
@@ -8042,25 +8042,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>5.32170931555485</v>
+        <v>23.0112155885352</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0323874018730251</v>
+        <v>0.654867205224065</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0234690096744761</v>
+        <v>0.0842403697280779</v>
       </c>
       <c r="F3" t="n">
-        <v>0.398616221203364</v>
+        <v>0.718076530923478</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0358073594535746</v>
+        <v>0.0163832994919434</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -8081,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0324037564406869</v>
+        <v>0.0106898124344595</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -8090,13 +8090,13 @@
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.181130178259826</v>
+        <v>5.92285325037109</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0557407530717782</v>
+        <v>0.15047072937636</v>
       </c>
     </row>
     <row r="4">
@@ -8104,7 +8104,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.143171989947972</v>
+        <v>0.0306174728849321</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -8113,7 +8113,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.39075091831807</v>
+        <v>0.0693662753742522</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -8122,7 +8122,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0446957110909868</v>
+        <v>0.00101138799319596</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -8134,31 +8134,31 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00616808018504241</v>
+        <v>0.000229860907544536</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0218498712375804</v>
+        <v>0.0122400933267465</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0855881827726838</v>
+        <v>0.00139640501333305</v>
       </c>
       <c r="P4" t="n">
-        <v>9.8830058224163</v>
+        <v>0.312133872877413</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.724325276938463</v>
+        <v>1.17137693136964</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.114537562875677</v>
+        <v>0.0152914968744002</v>
       </c>
     </row>
     <row r="5">
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08107466943245</v>
+        <v>18.9584278702809</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -8228,16 +8228,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>4.30416169105038</v>
+        <v>10.3314487429205</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0591087323750773</v>
+        <v>0.663457354578933</v>
       </c>
       <c r="E6" t="n">
-        <v>0.808305064236784</v>
+        <v>1.61059013648026</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -8246,43 +8246,43 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.336995503509883</v>
+        <v>0.0855928358473891</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0348287544177415</v>
+        <v>0.0133517083801127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0163281468527882</v>
+        <v>0.0123196922734373</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0354664610639938</v>
+        <v>0.0148352315334585</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0408787497097455</v>
+        <v>0.257036511568836</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0218762317698069</v>
+        <v>0.00715961174006043</v>
       </c>
       <c r="O6" t="n">
-        <v>0.37334762855574</v>
+        <v>0.0683710670672437</v>
       </c>
       <c r="P6" t="n">
-        <v>0.215429403202329</v>
+        <v>0.0763691918939779</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.266400725748762</v>
+        <v>4.83570497084748</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.503130241433217</v>
+        <v>0.75395226693303</v>
       </c>
     </row>
     <row r="7">
@@ -8290,61 +8290,61 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0279464845243789</v>
+        <v>0.0266053148107132</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0779659146035038</v>
+        <v>0.0171655444596044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0131020717300385</v>
+        <v>0.0583270363157942</v>
       </c>
       <c r="E7" t="n">
-        <v>0.555551922804633</v>
+        <v>0.439038858443711</v>
       </c>
       <c r="F7" t="n">
-        <v>0.138806166347838</v>
+        <v>0.0550525360313988</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>1.31369837200951</v>
+        <v>0.132335859149826</v>
       </c>
       <c r="I7" t="n">
-        <v>4.69627529857071</v>
+        <v>1.52448453865386</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00807623290846179</v>
+        <v>0.0012279376066483</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0328272690652914</v>
+        <v>0.0098235008531864</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0552043176561295</v>
+        <v>0.00915836798291857</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0451666587131768</v>
+        <v>0.11263769337651</v>
       </c>
       <c r="N7" t="n">
-        <v>0.060898699251084</v>
+        <v>0.00790484834279843</v>
       </c>
       <c r="O7" t="n">
-        <v>6.90869220200079</v>
+        <v>0.501791586550133</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0211596913724573</v>
+        <v>0.0138910441752089</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8042341025151</v>
+        <v>12.98930307736</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>24.9674239417424</v>
+        <v>14.8390375895749</v>
       </c>
     </row>
     <row r="8">
@@ -8361,7 +8361,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0453842090532627</v>
+        <v>0.356041971304338</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -8385,7 +8385,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0082167825639915</v>
+        <v>0.203416276044775</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -8400,13 +8400,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.227512495064972</v>
+        <v>16.2598425796739</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.00533733851806988</v>
+        <v>0.0314901600868316</v>
       </c>
     </row>
     <row r="9">
@@ -8417,22 +8417,22 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0.012084135795476</v>
+        <v>0.00819594292944278</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000517187041975205</v>
+        <v>0.0070926429197101</v>
       </c>
       <c r="E9" t="n">
-        <v>0.333098082138426</v>
+        <v>0.810925507153521</v>
       </c>
       <c r="F9" t="n">
-        <v>0.268001682702262</v>
+        <v>0.32744368145995</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.147800590084968</v>
+        <v>0.0458657575474586</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -8444,16 +8444,16 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0226676946800308</v>
+        <v>0.0115846501021932</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00862710878441555</v>
+        <v>0.0662768077275133</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.526913256905082</v>
+        <v>0.117895486754292</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -8462,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.04858930207089</v>
+        <v>23.2556728337197</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.08933357431704</v>
+        <v>1.99445118902248</v>
       </c>
     </row>
     <row r="10">
@@ -8479,13 +8479,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>0.00732019764533642</v>
+        <v>0.0106000556923561</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00162626592087759</v>
+        <v>0.0476161231894726</v>
       </c>
       <c r="E10" t="n">
-        <v>1.24877791201692</v>
+        <v>6.49076743561938</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -8494,28 +8494,28 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.04152739466161</v>
+        <v>1.35260075731509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00945685722628013</v>
+        <v>0.0201905822711545</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.49796573517011</v>
+        <v>0.98008451441229</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0446024601600937</v>
+        <v>0.73157209762483</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.591016340298615</v>
+        <v>0.282331642091643</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -8524,13 +8524,13 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.96169907967292</v>
+        <v>140.238232045314</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0313783853199431</v>
+        <v>0.122657787297263</v>
       </c>
     </row>
     <row r="11">
@@ -8541,13 +8541,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00639064873799212</v>
+        <v>0.00470182239216413</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0000402256588202937</v>
+        <v>0.000598413759002708</v>
       </c>
       <c r="E11" t="n">
-        <v>0.443774694658473</v>
+        <v>1.17195060316687</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -8556,10 +8556,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0.328869010584249</v>
+        <v>0.110706545415501</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00583172862287275</v>
+        <v>0.00632608830945719</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8571,13 +8571,13 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.185529000564732</v>
+        <v>1.54613017790328</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0.144408045007409</v>
+        <v>0.0350499487415872</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -8586,13 +8586,13 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.73196893919125</v>
+        <v>41.667891990078</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0111051075617906</v>
+        <v>0.0220558214032427</v>
       </c>
     </row>
     <row r="12">
@@ -8603,13 +8603,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0101088443673693</v>
+        <v>0.0134155744024672</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0.136055514016308</v>
+        <v>0.648111025443331</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -8618,28 +8618,28 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.598059088745874</v>
+        <v>0.363145720894372</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.49652006901814</v>
+        <v>0.455050115651503</v>
       </c>
       <c r="K12" t="n">
-        <v>0.160203912053011</v>
+        <v>0.288974556669237</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0311745345967168</v>
+        <v>0.468619892058597</v>
       </c>
       <c r="N12" t="n">
-        <v>0.837406385494679</v>
+        <v>0.65520431765613</v>
       </c>
       <c r="O12" t="n">
-        <v>0.190900391204916</v>
+        <v>0.0835774865073246</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -8648,13 +8648,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.01261839936512</v>
+        <v>43.9434078643022</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0101581604053588</v>
+        <v>0.0363916730917502</v>
       </c>
     </row>
     <row r="13">
@@ -8665,13 +8665,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0.85007247576637</v>
+        <v>0.0750486657155578</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1.13580295510116</v>
+        <v>0.359927902400462</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -8704,19 +8704,19 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.270014556040757</v>
+        <v>0.0152231027777321</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>32.1656907547204</v>
+        <v>92.8581572421778</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.00391691778342225</v>
+        <v>0.000933492151464703</v>
       </c>
     </row>
     <row r="14">
@@ -8724,16 +8724,16 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0000537432394699595</v>
+        <v>0.000394166338194718</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0045315509233035</v>
+        <v>0.007686243594797</v>
       </c>
       <c r="D14" t="n">
-        <v>0.00226412993931367</v>
+        <v>0.0776507686243595</v>
       </c>
       <c r="E14" t="n">
-        <v>0.299885387068064</v>
+        <v>1.82577847851793</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -8742,28 +8742,28 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>56.6662891233495</v>
+        <v>43.9765471028774</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00606815005352975</v>
+        <v>0.0151754040204966</v>
       </c>
       <c r="J14" t="n">
-        <v>0.411046604070253</v>
+        <v>0.481474182104848</v>
       </c>
       <c r="K14" t="n">
-        <v>0.359475693800912</v>
+        <v>0.828734726054395</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0304769800219959</v>
+        <v>0.585534095388254</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.61173466818025</v>
+        <v>0.901852581789515</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -8772,13 +8772,13 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.79213094377948</v>
+        <v>43.9343713046906</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0778648820902292</v>
+        <v>0.356523452897123</v>
       </c>
     </row>
     <row r="15">
@@ -8795,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0665872453798584</v>
+        <v>0.724505728244488</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8804,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.46886359630834</v>
+        <v>2.03721007883623</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8819,7 +8819,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.000564198553083062</v>
+        <v>0.019371810915628</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.364701531088344</v>
+        <v>36.1495602422815</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -8848,16 +8848,16 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>6.73623137840419</v>
+        <v>45.6117176128093</v>
       </c>
       <c r="C16" t="n">
-        <v>0.243541813724209</v>
+        <v>0.38136826783115</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.077593401640992</v>
+        <v>0.436135371179039</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -8866,19 +8866,19 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0159990329473419</v>
+        <v>0.0114628820960699</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00795952149878578</v>
+        <v>0.0183770014556041</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00252382278389431</v>
+        <v>0.0027292576419214</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00324853183458613</v>
+        <v>0.00691411935953421</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00400925212027756</v>
+        <v>0.00473071324599709</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -8887,22 +8887,22 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0123275160372178</v>
+        <v>0.00636826783114993</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0155093133816538</v>
+        <v>0.0724163027656478</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0373211884934075</v>
+        <v>1.91102620087336</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.010287289563054</v>
+        <v>0.0434861717612809</v>
       </c>
     </row>
     <row r="17">
@@ -8910,46 +8910,46 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2.07258115853925</v>
+        <v>3.00557244174265</v>
       </c>
       <c r="C17" t="n">
-        <v>0.605601113134816</v>
+        <v>0.203101862676331</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0419208830134347</v>
+        <v>0.284272465123529</v>
       </c>
       <c r="E17" t="n">
-        <v>0.551570283921929</v>
+        <v>0.663977866105526</v>
       </c>
       <c r="F17" t="n">
-        <v>1.94928492248979</v>
+        <v>1.17765567765568</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.670689619268727</v>
+        <v>0.102914815680773</v>
       </c>
       <c r="I17" t="n">
-        <v>0.218374594783519</v>
+        <v>0.107980671810459</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0156477012601447</v>
+        <v>0.00362403553892916</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0144474178959225</v>
+        <v>0.00658561296859169</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0252891287586739</v>
+        <v>0.00639077234821916</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0450435608470496</v>
+        <v>0.17110903281116</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0134016554986204</v>
+        <v>0.00264983243706648</v>
       </c>
       <c r="O17" t="n">
-        <v>0.861165048885645</v>
+        <v>0.0952770633621697</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -8958,13 +8958,13 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.988057411564827</v>
+        <v>10.8355155482815</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4628611844768</v>
+        <v>1.3243706647962</v>
       </c>
     </row>
     <row r="18">
@@ -9034,61 +9034,61 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2.47584355590209</v>
+        <v>27.6104285286185</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0526357068783714</v>
+        <v>0.135750674258316</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0763827795770491</v>
+        <v>3.98321845969434</v>
       </c>
       <c r="E19" t="n">
-        <v>0.190503616461092</v>
+        <v>1.7635600839077</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0505042882204263</v>
+        <v>0.234641893916692</v>
       </c>
       <c r="G19" t="n">
-        <v>0.00931186018374961</v>
+        <v>0.109080011986814</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0606947440383286</v>
+        <v>0.0716212166616722</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0313652431338291</v>
+        <v>0.119268804315253</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0112730751013946</v>
+        <v>0.0200779142942763</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00760840350732014</v>
+        <v>0.0266706622715014</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00771010023130301</v>
+        <v>0.0149835181300569</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0139921241164599</v>
+        <v>0.408750374587953</v>
       </c>
       <c r="N19" t="n">
-        <v>0.00413874655104454</v>
+        <v>0.00629307761462391</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0929846923950145</v>
+        <v>0.0791129757267006</v>
       </c>
       <c r="P19" t="n">
-        <v>0.389919941775837</v>
+        <v>0.64219358705424</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0133660665575559</v>
+        <v>0.102786934372191</v>
       </c>
       <c r="R19" t="n">
-        <v>0.0887208830147004</v>
+        <v>7.48216961342523</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.173592630994966</v>
+        <v>1.20857057237039</v>
       </c>
     </row>
     <row r="20">
@@ -9105,7 +9105,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.226403108501084</v>
+        <v>0.301043109640167</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -9135,7 +9135,7 @@
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.00457879167096662</v>
+        <v>0.000559559683346036</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9144,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.353877924485381</v>
+        <v>4.28661456190372</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
